--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,6 +1973,715 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129593951</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>459894</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6987074</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129593954</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>460015</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6986997</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129593949</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>460018</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6986990</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129593948</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>459885</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6987078</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129593947</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>460017</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6986992</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129593964</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91567</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>459893</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6987073</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129593953</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>460018</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6986999</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -1978,7 +1978,7 @@
         <v>129593951</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>129593954</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129593949</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129593948</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>129593947</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129593953</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -1978,7 +1978,7 @@
         <v>129593951</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>129593954</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129593949</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129593948</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>129593947</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91595</v>
+        <v>91601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129593953</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -1978,7 +1978,7 @@
         <v>129593951</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>129593954</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129593949</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129593948</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>129593947</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129593953</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -1978,7 +1978,7 @@
         <v>129593951</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>129593954</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129593949</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129593948</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>129593947</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129593953</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 39281-2025 artfynd.xlsx
+++ b/artfynd/A 39281-2025 artfynd.xlsx
@@ -1978,7 +1978,7 @@
         <v>129593951</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>129593954</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129593949</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129593948</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>129593947</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129593964</v>
       </c>
       <c r="B19" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129593953</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
